--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.76626334528418</v>
+        <v>4.02451779360868</v>
       </c>
       <c r="D2" t="n">
-        <v>22.17728965889314</v>
+        <v>3.603809569570136</v>
       </c>
       <c r="E2" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F2" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.93973946360743</v>
+        <v>3.240207662836208</v>
       </c>
       <c r="D3" t="n">
-        <v>54.49796122588237</v>
+        <v>8.855918699205885</v>
       </c>
       <c r="E3" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F3" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.43004951702932</v>
+        <v>5.757383046517266</v>
       </c>
       <c r="D4" t="n">
-        <v>13.23295549418616</v>
+        <v>2.150355267805251</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F4" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.96686329051455</v>
+        <v>3.244615284708615</v>
       </c>
       <c r="D5" t="n">
-        <v>12.72146927653127</v>
+        <v>2.067238757436332</v>
       </c>
       <c r="E5" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F5" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.04640919779088</v>
+        <v>4.232541494641018</v>
       </c>
       <c r="D6" t="n">
-        <v>80.27602650250448</v>
+        <v>13.04485430665698</v>
       </c>
       <c r="E6" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F6" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.43354245333047</v>
+        <v>1.857950648666202</v>
       </c>
       <c r="D7" t="n">
-        <v>11.99727509395774</v>
+        <v>1.949557202768133</v>
       </c>
       <c r="E7" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F7" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.55784926177324</v>
+        <v>4.640650505038151</v>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>1.54375</v>
       </c>
       <c r="E8" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F8" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.91240139811638</v>
+        <v>3.398265227193911</v>
       </c>
       <c r="D9" t="n">
-        <v>20.18043607061056</v>
+        <v>3.279320861474217</v>
       </c>
       <c r="E9" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F9" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.57506278853224</v>
+        <v>4.480947703136488</v>
       </c>
       <c r="D10" t="n">
-        <v>28.33668217035316</v>
+        <v>4.604710852682389</v>
       </c>
       <c r="E10" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F10" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.30885044186697</v>
+        <v>6.712688196803382</v>
       </c>
       <c r="D11" t="n">
-        <v>41.42764777295472</v>
+        <v>6.731992763105143</v>
       </c>
       <c r="E11" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F11" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.65840794048836</v>
+        <v>4.656991290329358</v>
       </c>
       <c r="D12" t="n">
-        <v>28.28024742079695</v>
+        <v>4.595540205879504</v>
       </c>
       <c r="E12" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F12" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.262225096603997</v>
+        <v>1.505111578198149</v>
       </c>
       <c r="D13" t="n">
-        <v>9.988189253386125</v>
+        <v>1.623080753675245</v>
       </c>
       <c r="E13" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F13" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.68718769362181</v>
+        <v>4.824168000213544</v>
       </c>
       <c r="D14" t="n">
-        <v>29.76295815529324</v>
+        <v>4.836480700235152</v>
       </c>
       <c r="E14" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F14" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.00928911433859</v>
+        <v>6.82650948108002</v>
       </c>
       <c r="D15" t="n">
-        <v>42.73136819957909</v>
+        <v>6.943847332431603</v>
       </c>
       <c r="E15" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F15" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>63.9834892111848</v>
+        <v>10.39731699681753</v>
       </c>
       <c r="D16" t="n">
-        <v>64.51962860787611</v>
+        <v>10.48443964877987</v>
       </c>
       <c r="E16" t="n">
-        <v>13.01452698837014</v>
+        <v>2.114860635610149</v>
       </c>
       <c r="F16" t="n">
-        <v>20.77550508021844</v>
+        <v>3.376019575535497</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
